--- a/work_request_forms/035_service_request_work_order--work_request_forms.xlsx
+++ b/work_request_forms/035_service_request_work_order--work_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'provider_1'}</t>
+          <t>provider_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Provider 1'}</t>
+          <t>Provider 1</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'provider_2'}</t>
+          <t>provider_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Provider 2'}</t>
+          <t>Provider 2</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'provider_3'}</t>
+          <t>provider_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Provider 3'}</t>
+          <t>Provider 3</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'type_1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Type 1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'type_2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Type 2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'type_3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Type 3'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
